--- a/TCLAutoTestTool/bin/自动化测试导入数据.xlsx
+++ b/TCLAutoTestTool/bin/自动化测试导入数据.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
     <t>序号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -89,6 +89,18 @@
   <si>
     <t>Boost电流
 (mA)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>55QM7K</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>L36</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>6+10</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -563,18 +575,42 @@
       <c r="A3" s="2">
         <v>2</v>
       </c>
-      <c r="B3" s="5"/>
-      <c r="C3" s="5"/>
-      <c r="D3" s="5"/>
-      <c r="E3" s="5"/>
-      <c r="F3" s="5"/>
-      <c r="G3" s="5"/>
-      <c r="H3" s="5"/>
-      <c r="I3" s="5"/>
-      <c r="J3" s="5"/>
-      <c r="K3" s="5"/>
-      <c r="L3" s="5"/>
-      <c r="M3" s="5"/>
+      <c r="B3" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="5">
+        <v>36</v>
+      </c>
+      <c r="D3" s="5">
+        <v>20</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F3" s="5">
+        <v>90</v>
+      </c>
+      <c r="G3" s="5">
+        <v>0</v>
+      </c>
+      <c r="H3" s="5">
+        <v>1.43</v>
+      </c>
+      <c r="I3" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="J3" s="5">
+        <v>9.5</v>
+      </c>
+      <c r="K3" s="5">
+        <v>10</v>
+      </c>
+      <c r="L3" s="5">
+        <v>45</v>
+      </c>
+      <c r="M3" s="5">
+        <v>65</v>
+      </c>
     </row>
     <row r="4" spans="1:13" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A4" s="2">

--- a/TCLAutoTestTool/bin/自动化测试导入数据.xlsx
+++ b/TCLAutoTestTool/bin/自动化测试导入数据.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="25">
   <si>
     <t>序号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -42,18 +42,6 @@
   </si>
   <si>
     <t>数据格式</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>65Q10MPro</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>L21</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>6+10</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -101,6 +89,45 @@
   </si>
   <si>
     <t>6+10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>65T6M</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>L50</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>65T5MPlus</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>L49</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>8+12</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>全白亮度
+（nites)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>L32亮度
+（nites)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Boost亮度
+（nites)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>65QM7K</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -108,7 +135,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -141,6 +168,15 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -150,7 +186,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -173,11 +209,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -193,6 +240,13 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -474,7 +528,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:P9"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="3"/>
@@ -487,9 +541,12 @@
     <col min="9" max="11" width="12.875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="11.625" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="14.75" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.25" customWidth="1"/>
+    <col min="15" max="15" width="14.375" customWidth="1"/>
+    <col min="16" max="16" width="15.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="40.5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:16" ht="40.5" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -506,45 +563,52 @@
         <v>4</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>5</v>
       </c>
       <c r="J1" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="K1" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="L1" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="M1" s="4" t="s">
-        <v>15</v>
+      <c r="N1" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="O1" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="P1" s="6" t="s">
+        <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A2" s="2">
-        <v>1</v>
-      </c>
+    <row r="2" spans="1:16" ht="20.25" x14ac:dyDescent="0.2">
+      <c r="A2" s="1"/>
       <c r="B2" s="5" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="C2" s="5">
-        <v>84</v>
+        <v>18</v>
       </c>
       <c r="D2" s="5">
-        <v>42</v>
+        <v>4</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="F2" s="5">
         <v>80</v>
@@ -556,99 +620,183 @@
         <v>1.25</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="J2" s="5">
-        <v>3.8</v>
+        <v>37.5</v>
       </c>
       <c r="K2" s="5">
-        <v>6.25</v>
+        <v>37.65</v>
       </c>
       <c r="L2" s="5">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="M2" s="5">
-        <v>60</v>
+        <v>50</v>
+      </c>
+      <c r="N2" s="8">
+        <v>500</v>
+      </c>
+      <c r="O2" s="8">
+        <v>550</v>
+      </c>
+      <c r="P2" s="8">
+        <v>600</v>
       </c>
     </row>
-    <row r="3" spans="1:13" ht="15.75" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:16" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A3" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B3" s="5" t="s">
         <v>16</v>
       </c>
       <c r="C3" s="5">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="D3" s="5">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E3" s="5" t="s">
         <v>17</v>
       </c>
       <c r="F3" s="5">
+        <v>80</v>
+      </c>
+      <c r="G3" s="5">
+        <v>1.25</v>
+      </c>
+      <c r="H3" s="5">
+        <v>1.25</v>
+      </c>
+      <c r="I3" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="J3" s="5">
+        <v>23</v>
+      </c>
+      <c r="K3" s="5">
+        <v>23.22</v>
+      </c>
+      <c r="L3" s="5">
+        <v>40</v>
+      </c>
+      <c r="M3" s="5">
+        <v>60</v>
+      </c>
+      <c r="N3" s="8">
+        <v>500</v>
+      </c>
+      <c r="O3" s="8">
+        <v>600</v>
+      </c>
+      <c r="P3" s="8">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="A4" s="2">
+        <v>4</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" s="5">
+        <v>36</v>
+      </c>
+      <c r="D4" s="5">
+        <v>20</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="F4" s="5">
         <v>90</v>
       </c>
-      <c r="G3" s="5">
+      <c r="G4" s="5">
         <v>0</v>
       </c>
-      <c r="H3" s="5">
+      <c r="H4" s="5">
         <v>1.43</v>
       </c>
-      <c r="I3" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="J3" s="5">
+      <c r="I4" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="J4" s="5">
         <v>9.5</v>
       </c>
-      <c r="K3" s="5">
+      <c r="K4" s="5">
         <v>10</v>
       </c>
-      <c r="L3" s="5">
+      <c r="L4" s="5">
         <v>45</v>
       </c>
-      <c r="M3" s="5">
+      <c r="M4" s="5">
         <v>65</v>
       </c>
+      <c r="N4" s="8">
+        <v>550</v>
+      </c>
+      <c r="O4" s="8">
+        <v>2000</v>
+      </c>
+      <c r="P4" s="8">
+        <v>2800</v>
+      </c>
     </row>
-    <row r="4" spans="1:13" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A4" s="2">
-        <v>3</v>
-      </c>
-      <c r="B4" s="5"/>
-      <c r="C4" s="5"/>
-      <c r="D4" s="5"/>
-      <c r="E4" s="5"/>
-      <c r="F4" s="5"/>
-      <c r="G4" s="5"/>
-      <c r="H4" s="5"/>
-      <c r="I4" s="5"/>
-      <c r="J4" s="5"/>
-      <c r="K4" s="5"/>
-      <c r="L4" s="5"/>
-      <c r="M4" s="5"/>
+    <row r="5" spans="1:16" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="A5" s="2">
+        <v>5</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" s="5">
+        <v>36</v>
+      </c>
+      <c r="D5" s="5">
+        <v>20</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="F5" s="5">
+        <v>90</v>
+      </c>
+      <c r="G5" s="5">
+        <v>0</v>
+      </c>
+      <c r="H5" s="5">
+        <v>1.43</v>
+      </c>
+      <c r="I5" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="J5" s="5">
+        <v>9.5</v>
+      </c>
+      <c r="K5" s="5">
+        <v>10</v>
+      </c>
+      <c r="L5" s="5">
+        <v>45</v>
+      </c>
+      <c r="M5" s="5">
+        <v>65</v>
+      </c>
+      <c r="N5" s="8">
+        <v>550</v>
+      </c>
+      <c r="O5" s="8">
+        <v>2000</v>
+      </c>
+      <c r="P5" s="8">
+        <v>2800</v>
+      </c>
     </row>
-    <row r="5" spans="1:13" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A5" s="2">
-        <v>4</v>
-      </c>
-      <c r="B5" s="5"/>
-      <c r="C5" s="5"/>
-      <c r="D5" s="5"/>
-      <c r="E5" s="5"/>
-      <c r="F5" s="5"/>
-      <c r="G5" s="5"/>
-      <c r="H5" s="5"/>
-      <c r="I5" s="5"/>
-      <c r="J5" s="5"/>
-      <c r="K5" s="5"/>
-      <c r="L5" s="5"/>
-      <c r="M5" s="5"/>
-    </row>
-    <row r="6" spans="1:13" ht="15.75" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A6" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B6" s="5"/>
       <c r="C6" s="5"/>
@@ -662,10 +810,13 @@
       <c r="K6" s="5"/>
       <c r="L6" s="5"/>
       <c r="M6" s="5"/>
+      <c r="N6" s="7"/>
+      <c r="O6" s="7"/>
+      <c r="P6" s="7"/>
     </row>
-    <row r="7" spans="1:13" ht="15.75" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A7" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B7" s="5"/>
       <c r="C7" s="5"/>
@@ -679,10 +830,13 @@
       <c r="K7" s="5"/>
       <c r="L7" s="5"/>
       <c r="M7" s="5"/>
+      <c r="N7" s="7"/>
+      <c r="O7" s="7"/>
+      <c r="P7" s="7"/>
     </row>
-    <row r="8" spans="1:13" ht="15.75" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:16" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A8" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B8" s="5"/>
       <c r="C8" s="5"/>
@@ -696,10 +850,13 @@
       <c r="K8" s="5"/>
       <c r="L8" s="5"/>
       <c r="M8" s="5"/>
+      <c r="N8" s="7"/>
+      <c r="O8" s="7"/>
+      <c r="P8" s="7"/>
     </row>
-    <row r="9" spans="1:13" ht="15.75" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:16" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A9" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B9" s="5"/>
       <c r="C9" s="5"/>
@@ -713,23 +870,9 @@
       <c r="K9" s="5"/>
       <c r="L9" s="5"/>
       <c r="M9" s="5"/>
-    </row>
-    <row r="10" spans="1:13" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A10" s="2">
-        <v>9</v>
-      </c>
-      <c r="B10" s="5"/>
-      <c r="C10" s="5"/>
-      <c r="D10" s="5"/>
-      <c r="E10" s="5"/>
-      <c r="F10" s="5"/>
-      <c r="G10" s="5"/>
-      <c r="H10" s="5"/>
-      <c r="I10" s="5"/>
-      <c r="J10" s="5"/>
-      <c r="K10" s="5"/>
-      <c r="L10" s="5"/>
-      <c r="M10" s="5"/>
+      <c r="N9" s="7"/>
+      <c r="O9" s="7"/>
+      <c r="P9" s="7"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/TCLAutoTestTool/bin/自动化测试导入数据.xlsx
+++ b/TCLAutoTestTool/bin/自动化测试导入数据.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="33">
   <si>
     <t>序号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -84,10 +84,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>L36</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>6+10</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -96,15 +92,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>L50</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>65T5MPlus</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>L49</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -127,7 +115,53 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>65QM7K</t>
+    <t>75QM7K</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>55Q9M_Uitra</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>75X11G</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>55C655Pro</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>8+12</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>L44</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>65C8L</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>6+10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>65QM7LPro</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>头码个数
+(Byte)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>尾码个数
+(Byte)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>65C12L</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -135,6 +169,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <numFmts count="1">
+    <numFmt numFmtId="176" formatCode="0.00_ "/>
+  </numFmts>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -178,12 +215,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="3">
@@ -224,7 +267,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -244,9 +287,20 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -528,25 +582,27 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:P9"/>
+  <dimension ref="A1:R11"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="3"/>
-    <col min="2" max="2" width="11.75" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.125" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="15.875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="14.75" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="27.75" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="30" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="15.5" bestFit="1" customWidth="1"/>
-    <col min="9" max="11" width="12.875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.75" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.25" customWidth="1"/>
-    <col min="15" max="15" width="14.375" customWidth="1"/>
-    <col min="16" max="16" width="15.375" customWidth="1"/>
+    <col min="9" max="9" width="12.875" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="12.875" customWidth="1"/>
+    <col min="12" max="13" width="12.875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.75" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.25" style="8" customWidth="1"/>
+    <col min="17" max="17" width="14.375" style="8" customWidth="1"/>
+    <col min="18" max="18" width="15.375" style="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="40.5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:18" ht="40.5" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -575,31 +631,39 @@
         <v>5</v>
       </c>
       <c r="J1" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="L1" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="M1" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="N1" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="4" t="s">
+      <c r="O1" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="O1" s="6" t="s">
-        <v>22</v>
-      </c>
       <c r="P1" s="6" t="s">
-        <v>23</v>
+        <v>18</v>
+      </c>
+      <c r="Q1" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="R1" s="6" t="s">
+        <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:16" ht="20.25" x14ac:dyDescent="0.2">
-      <c r="A2" s="1"/>
+    <row r="2" spans="1:18" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
       <c r="B2" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C2" s="5">
         <v>18</v>
@@ -607,8 +671,9 @@
       <c r="D2" s="5">
         <v>4</v>
       </c>
-      <c r="E2" s="5" t="s">
-        <v>19</v>
+      <c r="E2" s="5" t="str">
+        <f t="shared" ref="E2" si="0">"L"&amp;((IF(INT(SQRT(L2/O2)*100)&gt;50,50,INT(SQRT(L2/O2)*100)))-2)</f>
+        <v>L48</v>
       </c>
       <c r="F2" s="5">
         <v>80</v>
@@ -620,36 +685,42 @@
         <v>1.25</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="J2" s="5">
+        <v>4</v>
+      </c>
+      <c r="K2" s="5">
+        <v>6</v>
+      </c>
+      <c r="L2" s="5">
         <v>37.5</v>
       </c>
-      <c r="K2" s="5">
+      <c r="M2" s="5">
         <v>37.65</v>
       </c>
-      <c r="L2" s="5">
+      <c r="N2" s="5">
         <v>40</v>
       </c>
-      <c r="M2" s="5">
+      <c r="O2" s="5">
         <v>50</v>
       </c>
-      <c r="N2" s="8">
+      <c r="P2" s="9">
         <v>500</v>
       </c>
-      <c r="O2" s="8">
+      <c r="Q2" s="9">
         <v>550</v>
       </c>
-      <c r="P2" s="8">
+      <c r="R2" s="9">
         <v>600</v>
       </c>
     </row>
-    <row r="3" spans="1:16" ht="15.75" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:18" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A3" s="2">
         <v>3</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C3" s="5">
         <v>18</v>
@@ -658,7 +729,7 @@
         <v>10</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="F3" s="5">
         <v>80</v>
@@ -670,31 +741,37 @@
         <v>1.25</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="J3" s="5">
+        <v>4</v>
+      </c>
+      <c r="K3" s="5">
+        <v>6</v>
+      </c>
+      <c r="L3" s="5">
         <v>23</v>
       </c>
-      <c r="K3" s="5">
+      <c r="M3" s="5">
         <v>23.22</v>
       </c>
-      <c r="L3" s="5">
+      <c r="N3" s="5">
         <v>40</v>
       </c>
-      <c r="M3" s="5">
+      <c r="O3" s="5">
         <v>60</v>
       </c>
-      <c r="N3" s="8">
+      <c r="P3" s="9">
         <v>500</v>
       </c>
-      <c r="O3" s="8">
+      <c r="Q3" s="9">
         <v>600</v>
       </c>
-      <c r="P3" s="8">
+      <c r="R3" s="9">
         <v>800</v>
       </c>
     </row>
-    <row r="4" spans="1:16" ht="15.75" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:18" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A4" s="2">
         <v>4</v>
       </c>
@@ -707,8 +784,9 @@
       <c r="D4" s="5">
         <v>20</v>
       </c>
-      <c r="E4" s="5" t="s">
-        <v>14</v>
+      <c r="E4" s="5" t="str">
+        <f>"L"&amp;((IF(INT(SQRT(L4/O4)*100)&gt;50,50,INT(SQRT(L4/O4)*100)))-2)</f>
+        <v>L36</v>
       </c>
       <c r="F4" s="5">
         <v>90</v>
@@ -720,45 +798,52 @@
         <v>1.43</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J4" s="5">
+        <v>6</v>
+      </c>
+      <c r="K4" s="5">
+        <v>6</v>
+      </c>
+      <c r="L4" s="5">
         <v>9.5</v>
       </c>
-      <c r="K4" s="5">
+      <c r="M4" s="5">
         <v>10</v>
       </c>
-      <c r="L4" s="5">
+      <c r="N4" s="5">
         <v>45</v>
       </c>
-      <c r="M4" s="5">
+      <c r="O4" s="5">
         <v>65</v>
       </c>
-      <c r="N4" s="8">
+      <c r="P4" s="9">
         <v>550</v>
       </c>
-      <c r="O4" s="8">
+      <c r="Q4" s="9">
         <v>2000</v>
       </c>
-      <c r="P4" s="8">
+      <c r="R4" s="9">
         <v>2800</v>
       </c>
     </row>
-    <row r="5" spans="1:16" ht="15.75" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A5" s="2">
         <v>5</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C5" s="5">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="D5" s="5">
-        <v>20</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>14</v>
+        <v>26</v>
+      </c>
+      <c r="E5" s="5" t="str">
+        <f t="shared" ref="E5:E11" si="1">"L"&amp;((IF(INT(SQRT(L5/O5)*100)&gt;50,50,INT(SQRT(L5/O5)*100)))-2)</f>
+        <v>L35</v>
       </c>
       <c r="F5" s="5">
         <v>90</v>
@@ -770,109 +855,378 @@
         <v>1.43</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J5" s="5">
-        <v>9.5</v>
+        <v>6</v>
       </c>
       <c r="K5" s="5">
+        <v>6</v>
+      </c>
+      <c r="L5" s="5">
+        <v>9</v>
+      </c>
+      <c r="M5" s="5">
         <v>10</v>
       </c>
-      <c r="L5" s="5">
+      <c r="N5" s="5">
         <v>45</v>
       </c>
-      <c r="M5" s="5">
+      <c r="O5" s="5">
         <v>65</v>
       </c>
-      <c r="N5" s="8">
-        <v>550</v>
-      </c>
-      <c r="O5" s="8">
+      <c r="P5" s="9">
+        <v>500</v>
+      </c>
+      <c r="Q5" s="9">
         <v>2000</v>
       </c>
-      <c r="P5" s="8">
+      <c r="R5" s="9">
         <v>2800</v>
       </c>
     </row>
-    <row r="6" spans="1:16" ht="15.75" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A6" s="2">
         <v>6</v>
       </c>
-      <c r="B6" s="5"/>
-      <c r="C6" s="5"/>
-      <c r="D6" s="5"/>
-      <c r="E6" s="5"/>
-      <c r="F6" s="5"/>
-      <c r="G6" s="5"/>
-      <c r="H6" s="5"/>
-      <c r="I6" s="5"/>
-      <c r="J6" s="5"/>
-      <c r="K6" s="5"/>
-      <c r="L6" s="5"/>
-      <c r="M6" s="5"/>
-      <c r="N6" s="7"/>
-      <c r="O6" s="7"/>
-      <c r="P6" s="7"/>
+      <c r="B6" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" s="5">
+        <v>40</v>
+      </c>
+      <c r="D6" s="5">
+        <v>20</v>
+      </c>
+      <c r="E6" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>L29</v>
+      </c>
+      <c r="F6" s="5">
+        <v>80</v>
+      </c>
+      <c r="G6" s="5">
+        <v>1.25</v>
+      </c>
+      <c r="H6" s="5">
+        <v>1.25</v>
+      </c>
+      <c r="I6" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="J6" s="5">
+        <v>6</v>
+      </c>
+      <c r="K6" s="5">
+        <v>6</v>
+      </c>
+      <c r="L6" s="5">
+        <v>7.8</v>
+      </c>
+      <c r="M6" s="5">
+        <v>8.75</v>
+      </c>
+      <c r="N6" s="5">
+        <v>40</v>
+      </c>
+      <c r="O6" s="5">
+        <v>80</v>
+      </c>
+      <c r="P6" s="9">
+        <v>500</v>
+      </c>
+      <c r="Q6" s="9">
+        <v>1800</v>
+      </c>
+      <c r="R6" s="9">
+        <v>2500</v>
+      </c>
     </row>
-    <row r="7" spans="1:16" ht="15.75" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A7" s="2">
         <v>7</v>
       </c>
-      <c r="B7" s="5"/>
-      <c r="C7" s="5"/>
-      <c r="D7" s="5"/>
-      <c r="E7" s="5"/>
-      <c r="F7" s="5"/>
-      <c r="G7" s="5"/>
-      <c r="H7" s="5"/>
-      <c r="I7" s="5"/>
-      <c r="J7" s="5"/>
-      <c r="K7" s="5"/>
-      <c r="L7" s="5"/>
-      <c r="M7" s="5"/>
-      <c r="N7" s="7"/>
-      <c r="O7" s="7"/>
-      <c r="P7" s="7"/>
+      <c r="B7" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C7" s="5">
+        <v>72</v>
+      </c>
+      <c r="D7" s="5">
+        <v>42</v>
+      </c>
+      <c r="E7" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>L38</v>
+      </c>
+      <c r="F7" s="5">
+        <v>31.5</v>
+      </c>
+      <c r="G7" s="5">
+        <v>0</v>
+      </c>
+      <c r="H7" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="I7" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="J7" s="5">
+        <v>6</v>
+      </c>
+      <c r="K7" s="5">
+        <v>6</v>
+      </c>
+      <c r="L7" s="5">
+        <v>5.2</v>
+      </c>
+      <c r="M7" s="5">
+        <v>10</v>
+      </c>
+      <c r="N7" s="5">
+        <v>14</v>
+      </c>
+      <c r="O7" s="5">
+        <v>31.5</v>
+      </c>
+      <c r="P7" s="10">
+        <v>500</v>
+      </c>
+      <c r="Q7" s="10">
+        <v>2000</v>
+      </c>
+      <c r="R7" s="10">
+        <v>3000</v>
+      </c>
     </row>
-    <row r="8" spans="1:16" ht="15.75" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:18" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A8" s="2">
         <v>8</v>
       </c>
-      <c r="B8" s="5"/>
-      <c r="C8" s="5"/>
-      <c r="D8" s="5"/>
-      <c r="E8" s="5"/>
-      <c r="F8" s="5"/>
-      <c r="G8" s="5"/>
-      <c r="H8" s="5"/>
-      <c r="I8" s="5"/>
-      <c r="J8" s="5"/>
-      <c r="K8" s="5"/>
-      <c r="L8" s="5"/>
-      <c r="M8" s="5"/>
-      <c r="N8" s="7"/>
-      <c r="O8" s="7"/>
-      <c r="P8" s="7"/>
+      <c r="B8" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C8" s="5">
+        <v>12</v>
+      </c>
+      <c r="D8" s="5">
+        <v>7</v>
+      </c>
+      <c r="E8" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>L48</v>
+      </c>
+      <c r="F8" s="5">
+        <v>60</v>
+      </c>
+      <c r="G8" s="5">
+        <v>0</v>
+      </c>
+      <c r="H8" s="7">
+        <f>60/255</f>
+        <v>0.23529411764705882</v>
+      </c>
+      <c r="I8" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="J8" s="5">
+        <v>4</v>
+      </c>
+      <c r="K8" s="5">
+        <v>6</v>
+      </c>
+      <c r="L8" s="5">
+        <v>27</v>
+      </c>
+      <c r="M8" s="5">
+        <v>27</v>
+      </c>
+      <c r="N8" s="5">
+        <v>50</v>
+      </c>
+      <c r="O8" s="5">
+        <v>60</v>
+      </c>
+      <c r="P8" s="10">
+        <v>500</v>
+      </c>
+      <c r="Q8" s="10">
+        <v>600</v>
+      </c>
+      <c r="R8" s="10">
+        <v>700</v>
+      </c>
     </row>
-    <row r="9" spans="1:16" ht="15.75" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:18" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A9" s="2">
         <v>9</v>
       </c>
-      <c r="B9" s="5"/>
-      <c r="C9" s="5"/>
-      <c r="D9" s="5"/>
-      <c r="E9" s="5"/>
-      <c r="F9" s="5"/>
-      <c r="G9" s="5"/>
-      <c r="H9" s="5"/>
-      <c r="I9" s="5"/>
-      <c r="J9" s="5"/>
-      <c r="K9" s="5"/>
-      <c r="L9" s="5"/>
-      <c r="M9" s="5"/>
-      <c r="N9" s="7"/>
-      <c r="O9" s="7"/>
-      <c r="P9" s="7"/>
+      <c r="B9" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" s="5">
+        <v>60</v>
+      </c>
+      <c r="D9" s="5">
+        <v>34</v>
+      </c>
+      <c r="E9" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>L24</v>
+      </c>
+      <c r="F9" s="5">
+        <v>80</v>
+      </c>
+      <c r="G9" s="5">
+        <v>1.25</v>
+      </c>
+      <c r="H9" s="5">
+        <v>1.25</v>
+      </c>
+      <c r="I9" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="J9" s="5">
+        <v>6</v>
+      </c>
+      <c r="K9" s="5">
+        <v>6</v>
+      </c>
+      <c r="L9" s="5">
+        <v>4.5</v>
+      </c>
+      <c r="M9" s="5">
+        <v>6.25</v>
+      </c>
+      <c r="N9" s="5">
+        <v>35</v>
+      </c>
+      <c r="O9" s="5">
+        <v>65</v>
+      </c>
+      <c r="P9" s="10">
+        <v>500</v>
+      </c>
+      <c r="Q9" s="10">
+        <v>600</v>
+      </c>
+      <c r="R9" s="10">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="A10" s="2">
+        <v>10</v>
+      </c>
+      <c r="B10" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="C10" s="11">
+        <v>48</v>
+      </c>
+      <c r="D10" s="11">
+        <v>24</v>
+      </c>
+      <c r="E10" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>L29</v>
+      </c>
+      <c r="F10" s="5">
+        <v>80</v>
+      </c>
+      <c r="G10" s="5">
+        <v>1.25</v>
+      </c>
+      <c r="H10" s="5">
+        <v>1.25</v>
+      </c>
+      <c r="I10" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="J10" s="5">
+        <v>6</v>
+      </c>
+      <c r="K10" s="5">
+        <v>6</v>
+      </c>
+      <c r="L10" s="11">
+        <v>6.5</v>
+      </c>
+      <c r="M10" s="11">
+        <v>7.5</v>
+      </c>
+      <c r="N10" s="11">
+        <v>40</v>
+      </c>
+      <c r="O10" s="11">
+        <v>65</v>
+      </c>
+      <c r="P10" s="10">
+        <v>500</v>
+      </c>
+      <c r="Q10" s="10">
+        <v>600</v>
+      </c>
+      <c r="R10" s="10">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="A11" s="2">
+        <v>11</v>
+      </c>
+      <c r="B11" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="C11" s="11">
+        <v>60</v>
+      </c>
+      <c r="D11" s="11">
+        <v>34</v>
+      </c>
+      <c r="E11" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>L22</v>
+      </c>
+      <c r="F11" s="5">
+        <v>80</v>
+      </c>
+      <c r="G11" s="5">
+        <v>1.25</v>
+      </c>
+      <c r="H11" s="5">
+        <v>1.25</v>
+      </c>
+      <c r="I11" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="J11" s="5">
+        <v>14</v>
+      </c>
+      <c r="K11" s="5">
+        <v>0</v>
+      </c>
+      <c r="L11" s="11">
+        <v>4.05</v>
+      </c>
+      <c r="M11" s="11">
+        <v>6.25</v>
+      </c>
+      <c r="N11" s="11">
+        <v>35</v>
+      </c>
+      <c r="O11" s="11">
+        <v>65</v>
+      </c>
+      <c r="P11" s="10">
+        <v>500</v>
+      </c>
+      <c r="Q11" s="10">
+        <v>2000</v>
+      </c>
+      <c r="R11" s="10">
+        <v>3000</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/TCLAutoTestTool/bin/自动化测试导入数据.xlsx
+++ b/TCLAutoTestTool/bin/自动化测试导入数据.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="37">
   <si>
     <t>序号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -162,6 +162,22 @@
   </si>
   <si>
     <t>65C12L</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>65P8L</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>85T5MPlus</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>75X11G</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>85C12L</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -267,7 +283,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -300,6 +316,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -582,7 +601,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:R11"/>
+  <dimension ref="A1:R15"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="3"/>
@@ -842,7 +861,7 @@
         <v>26</v>
       </c>
       <c r="E5" s="5" t="str">
-        <f t="shared" ref="E5:E11" si="1">"L"&amp;((IF(INT(SQRT(L5/O5)*100)&gt;50,50,INT(SQRT(L5/O5)*100)))-2)</f>
+        <f t="shared" ref="E5:E14" si="1">"L"&amp;((IF(INT(SQRT(L5/O5)*100)&gt;50,50,INT(SQRT(L5/O5)*100)))-2)</f>
         <v>L35</v>
       </c>
       <c r="F5" s="5">
@@ -1225,6 +1244,234 @@
         <v>2000</v>
       </c>
       <c r="R11" s="10">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="A12" s="3">
+        <v>12</v>
+      </c>
+      <c r="B12" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="C12" s="12">
+        <v>18</v>
+      </c>
+      <c r="D12" s="12">
+        <v>4</v>
+      </c>
+      <c r="E12" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>L48</v>
+      </c>
+      <c r="F12" s="5">
+        <v>80</v>
+      </c>
+      <c r="G12" s="5">
+        <v>1.25</v>
+      </c>
+      <c r="H12" s="5">
+        <v>1.25</v>
+      </c>
+      <c r="I12" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J12" s="12">
+        <v>4</v>
+      </c>
+      <c r="K12" s="12">
+        <v>6</v>
+      </c>
+      <c r="L12" s="12">
+        <v>37.5</v>
+      </c>
+      <c r="M12" s="12">
+        <v>37.65</v>
+      </c>
+      <c r="N12" s="12">
+        <v>40</v>
+      </c>
+      <c r="O12" s="12">
+        <v>50</v>
+      </c>
+      <c r="P12" s="10">
+        <v>500</v>
+      </c>
+      <c r="Q12" s="10">
+        <v>600</v>
+      </c>
+      <c r="R12" s="10">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="A13" s="3">
+        <v>13</v>
+      </c>
+      <c r="B13" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="C13" s="12">
+        <v>28</v>
+      </c>
+      <c r="D13" s="12">
+        <v>4</v>
+      </c>
+      <c r="E13" s="12" t="str">
+        <f t="shared" si="1"/>
+        <v>L48</v>
+      </c>
+      <c r="F13" s="12">
+        <v>90</v>
+      </c>
+      <c r="G13" s="12">
+        <v>0</v>
+      </c>
+      <c r="H13" s="12">
+        <v>1.43</v>
+      </c>
+      <c r="I13" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J13" s="12">
+        <v>4</v>
+      </c>
+      <c r="K13" s="12">
+        <v>6</v>
+      </c>
+      <c r="L13" s="12">
+        <v>46</v>
+      </c>
+      <c r="M13" s="12">
+        <v>46.24</v>
+      </c>
+      <c r="N13" s="12">
+        <v>55</v>
+      </c>
+      <c r="O13" s="12">
+        <v>65</v>
+      </c>
+      <c r="P13" s="10">
+        <v>500</v>
+      </c>
+      <c r="Q13" s="10">
+        <v>600</v>
+      </c>
+      <c r="R13" s="10">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="A14" s="3">
+        <v>14</v>
+      </c>
+      <c r="B14" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="C14" s="12">
+        <v>36</v>
+      </c>
+      <c r="D14" s="12">
+        <v>42</v>
+      </c>
+      <c r="E14" s="12" t="str">
+        <f t="shared" si="1"/>
+        <v>L38</v>
+      </c>
+      <c r="F14" s="12">
+        <v>31.5</v>
+      </c>
+      <c r="G14" s="12">
+        <v>0</v>
+      </c>
+      <c r="H14" s="12">
+        <v>0.5</v>
+      </c>
+      <c r="I14" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="J14" s="12">
+        <v>6</v>
+      </c>
+      <c r="K14" s="12">
+        <v>0</v>
+      </c>
+      <c r="L14" s="12">
+        <v>5.2</v>
+      </c>
+      <c r="M14" s="12">
+        <v>10</v>
+      </c>
+      <c r="N14" s="12">
+        <v>14</v>
+      </c>
+      <c r="O14" s="12">
+        <v>31.5</v>
+      </c>
+      <c r="P14" s="8">
+        <v>500</v>
+      </c>
+      <c r="Q14" s="8">
+        <v>1000</v>
+      </c>
+      <c r="R14" s="8">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="A15" s="2">
+        <v>15</v>
+      </c>
+      <c r="B15" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="C15" s="11">
+        <v>80</v>
+      </c>
+      <c r="D15" s="11">
+        <v>40</v>
+      </c>
+      <c r="E15" s="5" t="str">
+        <f t="shared" ref="E15" si="2">"L"&amp;((IF(INT(SQRT(L15/O15)*100)&gt;50,50,INT(SQRT(L15/O15)*100)))-2)</f>
+        <v>L26</v>
+      </c>
+      <c r="F15" s="5">
+        <v>80</v>
+      </c>
+      <c r="G15" s="5">
+        <v>1.25</v>
+      </c>
+      <c r="H15" s="5">
+        <v>1.25</v>
+      </c>
+      <c r="I15" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="J15" s="5">
+        <v>6</v>
+      </c>
+      <c r="K15" s="5">
+        <v>6</v>
+      </c>
+      <c r="L15" s="11">
+        <v>5.2</v>
+      </c>
+      <c r="M15" s="11">
+        <v>6.25</v>
+      </c>
+      <c r="N15" s="11">
+        <v>35</v>
+      </c>
+      <c r="O15" s="11">
+        <v>65</v>
+      </c>
+      <c r="P15" s="10">
+        <v>500</v>
+      </c>
+      <c r="Q15" s="10">
+        <v>2000</v>
+      </c>
+      <c r="R15" s="10">
         <v>3000</v>
       </c>
     </row>
